--- a/analysis/tie_validation/review_sheet.xlsx
+++ b/analysis/tie_validation/review_sheet.xlsx
@@ -805,7 +805,7 @@
       </c>
       <c r="U2" s="5" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="V2" s="5" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AG2" s="5" t="inlineStr">
         <is>
-          <t>Reference error, Disfluency (fillers, repetitions, false starts)</t>
+          <t>Reference error, Disfluency</t>
         </is>
       </c>
       <c r="AH2" s="5" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="AG3" s="5" t="inlineStr">
         <is>
-          <t>Technical vocabulary (jargon, numbers, names)</t>
+          <t>Technical vocabulary</t>
         </is>
       </c>
       <c r="AH3" s="5" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="AG6" s="5" t="inlineStr">
         <is>
-          <t>Reference error, Disfluency (fillers, repetitions, false starts)</t>
+          <t>Reference error, Disfluency</t>
         </is>
       </c>
       <c r="AH6" s="5" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="T7" s="5" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="U7" s="5" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="AG7" s="5" t="inlineStr">
         <is>
-          <t>Reference error, Technical vocabulary (jargon, numbers, names)</t>
+          <t>Reference error, Number formatting</t>
         </is>
       </c>
       <c r="AH7" s="5" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="R8" s="5" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>18.60</t>
         </is>
       </c>
       <c r="S8" s="5" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="AG9" s="5" t="inlineStr">
         <is>
-          <t>Reference error, Technical vocabulary (jargon, numbers, names)</t>
+          <t>Reference error, Technical vocabulary</t>
         </is>
       </c>
       <c r="AH9" s="5" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="S10" s="5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="T10" s="5" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="AG10" s="5" t="inlineStr">
         <is>
-          <t>Reference error, Disfluency (fillers, repetitions, false starts)</t>
+          <t>Reference error, Disfluency</t>
         </is>
       </c>
       <c r="AH10" s="5" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="T11" s="5" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>30.30</t>
         </is>
       </c>
       <c r="U11" s="5" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="AG11" s="5" t="inlineStr">
         <is>
-          <t>Reference error, Technical vocabulary (jargon, numbers, names)</t>
+          <t>Reference error, Technical vocabulary</t>
         </is>
       </c>
       <c r="AH11" s="5" t="inlineStr">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="T13" s="5" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.10</t>
         </is>
       </c>
       <c r="U13" s="5" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="AG13" s="5" t="inlineStr">
         <is>
-          <t>Reference error, Disfluency (fillers, repetitions, false starts)</t>
+          <t>Reference error, Disfluency</t>
         </is>
       </c>
       <c r="AH13" s="5" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="AG14" s="5" t="inlineStr">
         <is>
-          <t>Reference error, Disfluency (fillers, repetitions, false starts)</t>
+          <t>Reference error, Disfluency</t>
         </is>
       </c>
       <c r="AH14" s="5" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AG15" s="5" t="inlineStr">
         <is>
-          <t>Misalignment (wrong clip boundary)</t>
+          <t>Misalignment</t>
         </is>
       </c>
       <c r="AH15" s="5" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="S16" s="5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="T16" s="5" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="AG16" s="5" t="inlineStr">
         <is>
-          <t>Misalignment (wrong clip boundary)</t>
+          <t>Misalignment</t>
         </is>
       </c>
       <c r="AH16" s="5" t="inlineStr">
@@ -3515,9 +3515,8 @@
       </c>
       <c r="Z17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">By what is the concentration of Bn⁺ in the solution?
-So, Rₙ⁻Bn⁺ (resin) means activity of Bn⁺ in the resin, and Bn⁺ (S) means activity of Bn⁺ in the solution.
-</t>
+          <t>By what is the concentration of Bn⁺ in the solution?
+So, Rₙ⁻Bn⁺ (resin) means activity of Bn⁺ in the resin, and Bn⁺ (S) means activity of Bn⁺ in the solution.</t>
         </is>
       </c>
       <c r="AA17" s="5" t="inlineStr">
@@ -3552,7 +3551,7 @@
       </c>
       <c r="AG17" s="5" t="inlineStr">
         <is>
-          <t>Misalignment (wrong clip boundary)</t>
+          <t>Misalignment</t>
         </is>
       </c>
       <c r="AH17" s="5" t="inlineStr">
@@ -3736,7 +3735,7 @@
       </c>
       <c r="AG18" s="5" t="inlineStr">
         <is>
-          <t>Reference error, Technical vocabulary (jargon, numbers, names)</t>
+          <t>Reference error, Technical vocabulary</t>
         </is>
       </c>
       <c r="AH18" s="5" t="inlineStr">
@@ -4058,13 +4057,12 @@
       </c>
       <c r="Z20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">I won't say assumption, but it is an abstraction.
+          <t>I won't say assumption, but it is an abstraction.
 We'll talk about how it affects our analysis.
 As many number of processors as you need, which means it is valid for a single processor machine or even millions of processors.
 Yes.
 Ahmm.
-So, one is the amount of resources, how much memory I have, how much local versus shared.
-</t>
+So, one is the amount of resources, how much memory I have, how much local versus shared.</t>
         </is>
       </c>
       <c r="AA20" s="5" t="inlineStr">
@@ -4206,7 +4204,7 @@
       </c>
       <c r="S21" s="5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="T21" s="5" t="inlineStr">
@@ -4278,7 +4276,7 @@
       </c>
       <c r="AG21" s="5" t="inlineStr">
         <is>
-          <t>Technical vocabulary (jargon, numbers, names)</t>
+          <t>Technical vocabulary</t>
         </is>
       </c>
       <c r="AH21" s="5" t="inlineStr"/>
@@ -4366,32 +4364,32 @@
       </c>
       <c r="P22" s="5" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="Q22" s="5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="T22" s="5" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="U22" s="5" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="V22" s="5" t="inlineStr">
@@ -4570,7 +4568,7 @@
       </c>
       <c r="U23" s="5" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>33.10</t>
         </is>
       </c>
       <c r="V23" s="5" t="inlineStr">
@@ -4631,7 +4629,7 @@
       </c>
       <c r="AG23" s="5" t="inlineStr">
         <is>
-          <t>Reference error, Technical vocabulary (jargon, numbers, names)</t>
+          <t>Reference error, Technical vocabulary</t>
         </is>
       </c>
       <c r="AH23" s="5" t="inlineStr">
@@ -4723,32 +4721,32 @@
       </c>
       <c r="P24" s="5" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>35.00</t>
         </is>
       </c>
       <c r="Q24" s="5" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="T24" s="5" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>27.50</t>
         </is>
       </c>
       <c r="U24" s="5" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.50</t>
         </is>
       </c>
       <c r="V24" s="5" t="inlineStr">
@@ -4925,7 +4923,7 @@
       </c>
       <c r="T25" s="5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="U25" s="5" t="inlineStr">
@@ -4991,7 +4989,7 @@
       </c>
       <c r="AG25" s="5" t="inlineStr">
         <is>
-          <t>Reference error, Technical vocabulary (jargon, numbers, names)</t>
+          <t>Reference error, Technical vocabulary</t>
         </is>
       </c>
       <c r="AH25" s="5" t="inlineStr">
@@ -5103,7 +5101,7 @@
       </c>
       <c r="T26" s="5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="U26" s="5" t="inlineStr">
@@ -5281,7 +5279,7 @@
       </c>
       <c r="T27" s="5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="U27" s="5" t="inlineStr">
@@ -5440,32 +5438,32 @@
       </c>
       <c r="P28" s="5" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="Q28" s="5" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>24.00</t>
         </is>
       </c>
       <c r="R28" s="5" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="S28" s="5" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="T28" s="5" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="U28" s="5" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.40</t>
         </is>
       </c>
       <c r="V28" s="5" t="inlineStr">
@@ -5619,32 +5617,32 @@
       </c>
       <c r="P29" s="5" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="Q29" s="5" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="R29" s="5" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="S29" s="5" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="T29" s="5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="U29" s="5" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="V29" s="5" t="inlineStr">
@@ -6066,7 +6064,7 @@
       </c>
       <c r="AG31" s="5" t="inlineStr">
         <is>
-          <t>Misalignment (wrong clip boundary)</t>
+          <t>Misalignment</t>
         </is>
       </c>
       <c r="AH31" s="5" t="inlineStr">
@@ -6158,32 +6156,32 @@
       </c>
       <c r="P32" s="5" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="Q32" s="5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="R32" s="5" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.50</t>
         </is>
       </c>
       <c r="S32" s="5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="T32" s="5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="U32" s="5" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="V32" s="5" t="inlineStr">
@@ -6243,7 +6241,7 @@
       </c>
       <c r="AG32" s="5" t="inlineStr">
         <is>
-          <t>Misalignment (wrong clip boundary)</t>
+          <t>Misalignment</t>
         </is>
       </c>
       <c r="AH32" s="5" t="inlineStr">
@@ -6355,7 +6353,7 @@
       </c>
       <c r="T33" s="5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="U33" s="5" t="inlineStr">
@@ -6540,7 +6538,7 @@
       </c>
       <c r="U34" s="5" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>15.89</t>
         </is>
       </c>
       <c r="V34" s="5" t="inlineStr">
@@ -6705,7 +6703,7 @@
       </c>
       <c r="R35" s="5" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="S35" s="5" t="inlineStr">
@@ -6715,7 +6713,7 @@
       </c>
       <c r="T35" s="5" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="U35" s="5" t="inlineStr">
@@ -6880,22 +6878,22 @@
       </c>
       <c r="Q36" s="5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="R36" s="5" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="S36" s="5" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="T36" s="5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="U36" s="5" t="inlineStr">
@@ -6925,8 +6923,7 @@
       </c>
       <c r="Z36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Example, for hollow shaft, we can see that this comes out to be equal to Td₀/2, and Iₚ will be...
-</t>
+          <t>Example, for hollow shaft, we can see that this comes out to be equal to Td₀/2, and Iₚ will be...</t>
         </is>
       </c>
       <c r="AA36" s="5" t="inlineStr">
@@ -7140,7 +7137,7 @@
       </c>
       <c r="AG37" s="5" t="inlineStr">
         <is>
-          <t>Reference error, Technical vocabulary (jargon, numbers, names), Disfluency (fillers, repetitions, false starts)</t>
+          <t>Reference error, Technical vocabulary, Disfluency</t>
         </is>
       </c>
       <c r="AH37" s="5" t="inlineStr">
@@ -7498,7 +7495,7 @@
       </c>
       <c r="AG39" s="5" t="inlineStr">
         <is>
-          <t>Reference error, Disfluency (fillers, repetitions, false starts)</t>
+          <t>Reference error, Disfluency</t>
         </is>
       </c>
       <c r="AH39" s="5" t="inlineStr">
@@ -7680,7 +7677,7 @@
       </c>
       <c r="AG40" s="5" t="inlineStr">
         <is>
-          <t>Reference error, Technical vocabulary (jargon, numbers, names)</t>
+          <t>Reference error, Technical vocabulary</t>
         </is>
       </c>
       <c r="AH40" s="5" t="inlineStr">
@@ -7792,7 +7789,7 @@
       </c>
       <c r="T41" s="5" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>12.70</t>
         </is>
       </c>
       <c r="U41" s="5" t="inlineStr">
@@ -7953,7 +7950,7 @@
       </c>
       <c r="P42" s="5" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>12.90</t>
         </is>
       </c>
       <c r="Q42" s="5" t="inlineStr">
@@ -7973,7 +7970,7 @@
       </c>
       <c r="T42" s="5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="U42" s="5" t="inlineStr">
@@ -8147,7 +8144,7 @@
       </c>
       <c r="S43" s="5" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="T43" s="5" t="inlineStr">
@@ -8221,7 +8218,7 @@
       </c>
       <c r="AG43" s="5" t="inlineStr">
         <is>
-          <t>Reference error, Technical vocabulary (jargon, numbers, names)</t>
+          <t>Reference error, Technical vocabulary</t>
         </is>
       </c>
       <c r="AH43" s="5" t="inlineStr">
@@ -8401,7 +8398,7 @@
       </c>
       <c r="AG44" s="5" t="inlineStr">
         <is>
-          <t>Reference error, Technical vocabulary (jargon, numbers, names)</t>
+          <t>Reference error, Technical vocabulary</t>
         </is>
       </c>
       <c r="AH44" s="5" t="inlineStr">
@@ -8493,32 +8490,32 @@
       </c>
       <c r="P45" s="5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="Q45" s="5" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="R45" s="5" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="S45" s="5" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>32.00</t>
         </is>
       </c>
       <c r="T45" s="5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="U45" s="5" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.60</t>
         </is>
       </c>
       <c r="V45" s="5" t="inlineStr">
@@ -8580,7 +8577,7 @@
       </c>
       <c r="AG45" s="5" t="inlineStr">
         <is>
-          <t>Reference error, Technical vocabulary (jargon, numbers, names)</t>
+          <t>Reference error, Technical vocabulary</t>
         </is>
       </c>
       <c r="AH45" s="5" t="inlineStr">
@@ -8762,7 +8759,7 @@
       </c>
       <c r="AG46" s="5" t="inlineStr">
         <is>
-          <t>Reference error, Technical vocabulary (jargon, numbers, names)</t>
+          <t>Reference error, Technical vocabulary</t>
         </is>
       </c>
       <c r="AH46" s="5" t="inlineStr">

--- a/analysis/tie_validation/review_sheet.xlsx
+++ b/analysis/tie_validation/review_sheet.xlsx
@@ -171,15 +171,21 @@
     <comment ref="AG1" authorId="0" shapeId="0">
       <text>
         <t>Free text. Pick from these, comma-separated if more than one applies:
-- Noise / audio quality
-- Speed (fast or slow / unclear)
+- Reference error
+- Misalignment
+- Truncated audio
+- Disfluency
+- Number formatting
+- Technical vocabulary
+- Acronym or code
+- Hindi named entity
+- Indian-language named entity
+- Foreign named entity
+- English name or rare word
+- Brand or product name
 - Accent / pronunciation
-- Technical vocabulary (jargon, numbers, names)
-- Disfluency (fillers, repetitions, false starts)
-- Code-switching (non-English words)
-- Reference error
-- Misalignment (wrong clip boundary)
-- Other</t>
+- Spelling variant
+- Short utterance</t>
       </text>
     </comment>
     <comment ref="AH1" authorId="0" shapeId="0">
